--- a/Notes and data for listed articles/(row 6) data for 2023 Ni et al./raw_data/data_for_discrimination_index.xlsx
+++ b/Notes and data for listed articles/(row 6) data for 2023 Ni et al./raw_data/data_for_discrimination_index.xlsx
@@ -147,7 +147,7 @@
     <xdr:ext cx="3781425" cy="3152775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -203,7 +203,7 @@
     <xdr:ext cx="3571875" cy="2686050"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -231,7 +231,7 @@
     <xdr:ext cx="3838575" cy="2324100"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -259,7 +259,7 @@
     <xdr:ext cx="3571875" cy="2828925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -287,7 +287,7 @@
     <xdr:ext cx="3781425" cy="2143125"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Notes and data for listed articles/(row 6) data for 2023 Ni et al./raw_data/data_for_discrimination_index.xlsx
+++ b/Notes and data for listed articles/(row 6) data for 2023 Ni et al./raw_data/data_for_discrimination_index.xlsx
@@ -147,7 +147,7 @@
     <xdr:ext cx="3781425" cy="3152775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -175,7 +175,7 @@
     <xdr:ext cx="3838575" cy="2362200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -259,7 +259,7 @@
     <xdr:ext cx="3571875" cy="2828925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -287,7 +287,7 @@
     <xdr:ext cx="3781425" cy="2143125"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
